--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261013.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261013.xlsx
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>202612ESZ6</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>11,437</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>202612ESZ6</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13,352</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>13,352</t>
+          <t>11,437</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
